--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/117.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/117.xlsx
@@ -426,13 +426,13 @@
         <v>-8.619511522236694</v>
       </c>
       <c r="E2">
-        <v>-22.42074406865</v>
+        <v>-24.44371756277852</v>
       </c>
       <c r="F2">
-        <v>-3.695384407669228</v>
+        <v>-3.890052404061918</v>
       </c>
       <c r="G2">
-        <v>-13.95409460742735</v>
+        <v>-15.39125373948083</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.497314285368654</v>
       </c>
       <c r="E3">
-        <v>-23.0739492734124</v>
+        <v>-25.00470945132273</v>
       </c>
       <c r="F3">
-        <v>-3.537590357844756</v>
+        <v>-3.727887887820275</v>
       </c>
       <c r="G3">
-        <v>-13.84565934356129</v>
+        <v>-15.1731516888081</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.310204124296822</v>
       </c>
       <c r="E4">
-        <v>-23.94293173616629</v>
+        <v>-25.60081059884841</v>
       </c>
       <c r="F4">
-        <v>-3.498085516405248</v>
+        <v>-3.774246641150547</v>
       </c>
       <c r="G4">
-        <v>-13.73718269787599</v>
+        <v>-14.25839498757884</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.065896613021838</v>
       </c>
       <c r="E5">
-        <v>-23.97524692668502</v>
+        <v>-25.99728302669396</v>
       </c>
       <c r="F5">
-        <v>-3.724157749405469</v>
+        <v>-3.711929389805343</v>
       </c>
       <c r="G5">
-        <v>-13.88757747117954</v>
+        <v>-15.11056417011541</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.754615825291422</v>
       </c>
       <c r="E6">
-        <v>-24.04931464755448</v>
+        <v>-25.35592883840963</v>
       </c>
       <c r="F6">
-        <v>-3.576355467193565</v>
+        <v>-3.659469710553453</v>
       </c>
       <c r="G6">
-        <v>-14.16706696778697</v>
+        <v>-15.10401260049319</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.382069633163428</v>
       </c>
       <c r="E7">
-        <v>-24.23906223694987</v>
+        <v>-26.28647137682379</v>
       </c>
       <c r="F7">
-        <v>-3.339370322028862</v>
+        <v>-3.580858472395183</v>
       </c>
       <c r="G7">
-        <v>-13.73568467601947</v>
+        <v>-15.08834875427413</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.946736041141949</v>
       </c>
       <c r="E8">
-        <v>-25.00812844919852</v>
+        <v>-27.04094684581972</v>
       </c>
       <c r="F8">
-        <v>-3.54504235100034</v>
+        <v>-3.631913240531925</v>
       </c>
       <c r="G8">
-        <v>-13.78043166480103</v>
+        <v>-14.64116191810215</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.446928801133314</v>
       </c>
       <c r="E9">
-        <v>-25.55266386319886</v>
+        <v>-27.07931660608671</v>
       </c>
       <c r="F9">
-        <v>-3.313492124365406</v>
+        <v>-3.555072223513437</v>
       </c>
       <c r="G9">
-        <v>-14.02489890014851</v>
+        <v>-14.89762988102949</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.887955251863175</v>
       </c>
       <c r="E10">
-        <v>-25.79914870343636</v>
+        <v>-27.46204964379299</v>
       </c>
       <c r="F10">
-        <v>-3.458834983758399</v>
+        <v>-3.895292656252027</v>
       </c>
       <c r="G10">
-        <v>-13.66143907121023</v>
+        <v>-14.78110033331991</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.282388273773922</v>
       </c>
       <c r="E11">
-        <v>-26.60975913623138</v>
+        <v>-28.02604843907829</v>
       </c>
       <c r="F11">
-        <v>-3.402867996923056</v>
+        <v>-3.521782622697133</v>
       </c>
       <c r="G11">
-        <v>-13.31983546392223</v>
+        <v>-14.45615539118552</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.644373589939974</v>
       </c>
       <c r="E12">
-        <v>-27.60895334060181</v>
+        <v>-29.59489297429561</v>
       </c>
       <c r="F12">
-        <v>-3.308885573238438</v>
+        <v>-3.367836339458664</v>
       </c>
       <c r="G12">
-        <v>-13.03758497233504</v>
+        <v>-14.53684497288694</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-3.989561691987403</v>
       </c>
       <c r="E13">
-        <v>-27.72012284901611</v>
+        <v>-29.2525810955818</v>
       </c>
       <c r="F13">
-        <v>-3.086616374984469</v>
+        <v>-3.330629389194522</v>
       </c>
       <c r="G13">
-        <v>-12.90736135300227</v>
+        <v>-14.32887650210993</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-3.347390944252545</v>
       </c>
       <c r="E14">
-        <v>-28.03444875836252</v>
+        <v>-30.29873104693778</v>
       </c>
       <c r="F14">
-        <v>-3.118366040798968</v>
+        <v>-3.276565990650812</v>
       </c>
       <c r="G14">
-        <v>-12.55258674028628</v>
+        <v>-13.54930427270404</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.740576073333208</v>
       </c>
       <c r="E15">
-        <v>-29.75639420706817</v>
+        <v>-30.89522617170212</v>
       </c>
       <c r="F15">
-        <v>-2.980452808641684</v>
+        <v>-3.144404113371165</v>
       </c>
       <c r="G15">
-        <v>-11.94369465197582</v>
+        <v>-13.75903395370795</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.187354126836992</v>
       </c>
       <c r="E16">
-        <v>-30.04567086244114</v>
+        <v>-31.44799435144841</v>
       </c>
       <c r="F16">
-        <v>-2.62578564839827</v>
+        <v>-3.068707071735944</v>
       </c>
       <c r="G16">
-        <v>-11.90231614328047</v>
+        <v>-13.45529636629812</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.706916913006406</v>
       </c>
       <c r="E17">
-        <v>-30.58704993005813</v>
+        <v>-31.98735371965798</v>
       </c>
       <c r="F17">
-        <v>-2.833787874873823</v>
+        <v>-2.659530022918711</v>
       </c>
       <c r="G17">
-        <v>-11.44449086901804</v>
+        <v>-13.13087614563171</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.313022579586983</v>
       </c>
       <c r="E18">
-        <v>-31.28582516875973</v>
+        <v>-32.29157886773027</v>
       </c>
       <c r="F18">
-        <v>-2.44416940880409</v>
+        <v>-2.510878664118937</v>
       </c>
       <c r="G18">
-        <v>-10.76145249226453</v>
+        <v>-12.55725129895111</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.010605346899336</v>
       </c>
       <c r="E19">
-        <v>-32.06617860247249</v>
+        <v>-33.28473661624849</v>
       </c>
       <c r="F19">
-        <v>-2.133610327657541</v>
+        <v>-2.295468347960148</v>
       </c>
       <c r="G19">
-        <v>-10.73843757967552</v>
+        <v>-12.00389030151639</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.7972789639202132</v>
       </c>
       <c r="E20">
-        <v>-32.46301783671266</v>
+        <v>-34.66919074682149</v>
       </c>
       <c r="F20">
-        <v>-2.281681829275356</v>
+        <v>-2.546659165715459</v>
       </c>
       <c r="G20">
-        <v>-10.3884069787173</v>
+        <v>-11.63888941362958</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.6723483953128706</v>
       </c>
       <c r="E21">
-        <v>-32.92286852253256</v>
+        <v>-34.94308191175341</v>
       </c>
       <c r="F21">
-        <v>-1.928797315682766</v>
+        <v>-2.190418107406725</v>
       </c>
       <c r="G21">
-        <v>-10.52537417931356</v>
+        <v>-11.81572882470083</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-0.6282629470318812</v>
       </c>
       <c r="E22">
-        <v>-33.32881451800215</v>
+        <v>-35.15068300992404</v>
       </c>
       <c r="F22">
-        <v>-1.893233846345778</v>
+        <v>-2.067528974834016</v>
       </c>
       <c r="G22">
-        <v>-10.00049711569874</v>
+        <v>-11.01761588500226</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-0.653940774036777</v>
       </c>
       <c r="E23">
-        <v>-34.16704411376995</v>
+        <v>-35.60467158614101</v>
       </c>
       <c r="F23">
-        <v>-1.655274541115384</v>
+        <v>-2.342251225400652</v>
       </c>
       <c r="G23">
-        <v>-9.783672935604169</v>
+        <v>-10.99773605903894</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-0.7394062896777621</v>
       </c>
       <c r="E24">
-        <v>-34.48393766787871</v>
+        <v>-36.01671290762493</v>
       </c>
       <c r="F24">
-        <v>-1.684879563724035</v>
+        <v>-2.009819931350586</v>
       </c>
       <c r="G24">
-        <v>-9.938527013749118</v>
+        <v>-10.51603181980174</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-0.8758081911993603</v>
       </c>
       <c r="E25">
-        <v>-35.21178570970954</v>
+        <v>-36.33635524545635</v>
       </c>
       <c r="F25">
-        <v>-1.597656618046261</v>
+        <v>-1.998288228736214</v>
       </c>
       <c r="G25">
-        <v>-9.915200909879413</v>
+        <v>-11.37910759461744</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.055844735032301</v>
       </c>
       <c r="E26">
-        <v>-35.34630403010739</v>
+        <v>-36.20723033760163</v>
       </c>
       <c r="F26">
-        <v>-1.246722909687265</v>
+        <v>-1.784245547159447</v>
       </c>
       <c r="G26">
-        <v>-9.852009216625806</v>
+        <v>-10.89102724467161</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.272130441517299</v>
       </c>
       <c r="E27">
-        <v>-35.32260652562525</v>
+        <v>-36.32544162309786</v>
       </c>
       <c r="F27">
-        <v>-1.313363410507679</v>
+        <v>-1.887421192280334</v>
       </c>
       <c r="G27">
-        <v>-9.805688063440323</v>
+        <v>-11.85708747012295</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-1.517469857536074</v>
       </c>
       <c r="E28">
-        <v>-35.46490023589427</v>
+        <v>-37.13801967784921</v>
       </c>
       <c r="F28">
-        <v>-1.553037436261868</v>
+        <v>-1.828275759720449</v>
       </c>
       <c r="G28">
-        <v>-9.655902430515997</v>
+        <v>-11.90587497973519</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-1.789294730459443</v>
       </c>
       <c r="E29">
-        <v>-35.77786081032736</v>
+        <v>-35.99061984039273</v>
       </c>
       <c r="F29">
-        <v>-1.408336561606045</v>
+        <v>-1.788404779888903</v>
       </c>
       <c r="G29">
-        <v>-9.910456898121637</v>
+        <v>-11.28928918359147</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.085311384576749</v>
       </c>
       <c r="E30">
-        <v>-34.95155468662176</v>
+        <v>-37.16458597061521</v>
       </c>
       <c r="F30">
-        <v>-1.336165880004541</v>
+        <v>-1.790909762914969</v>
       </c>
       <c r="G30">
-        <v>-10.32826098735982</v>
+        <v>-11.30500434326639</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.402245707548039</v>
       </c>
       <c r="E31">
-        <v>-34.74521703269927</v>
+        <v>-35.66860911065531</v>
       </c>
       <c r="F31">
-        <v>-1.573652187447937</v>
+        <v>-1.980264610786102</v>
       </c>
       <c r="G31">
-        <v>-9.66665839297309</v>
+        <v>-12.00005337923638</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-2.739839394088147</v>
       </c>
       <c r="E32">
-        <v>-34.43777893231852</v>
+        <v>-35.24175967916631</v>
       </c>
       <c r="F32">
-        <v>-1.468240778706894</v>
+        <v>-1.988168064176212</v>
       </c>
       <c r="G32">
-        <v>-9.936795598432079</v>
+        <v>-11.59049916948206</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-3.098639928620474</v>
       </c>
       <c r="E33">
-        <v>-34.63664686836537</v>
+        <v>-36.27454610372565</v>
       </c>
       <c r="F33">
-        <v>-1.581440497769058</v>
+        <v>-2.001388807924892</v>
       </c>
       <c r="G33">
-        <v>-10.61932746171808</v>
+        <v>-11.66976687187437</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.475291193931611</v>
       </c>
       <c r="E34">
-        <v>-33.6971855003931</v>
+        <v>-34.87084822285706</v>
       </c>
       <c r="F34">
-        <v>-1.512415955563386</v>
+        <v>-1.815307668029623</v>
       </c>
       <c r="G34">
-        <v>-10.62204210906028</v>
+        <v>-11.54725351310256</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.861157299862798</v>
       </c>
       <c r="E35">
-        <v>-33.82183627592823</v>
+        <v>-34.68857940828533</v>
       </c>
       <c r="F35">
-        <v>-1.41982767421768</v>
+        <v>-1.797262512527038</v>
       </c>
       <c r="G35">
-        <v>-10.6500393926859</v>
+        <v>-11.71632638433868</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.252113480405442</v>
       </c>
       <c r="E36">
-        <v>-32.82301567066342</v>
+        <v>-35.2127683885692</v>
       </c>
       <c r="F36">
-        <v>-1.537732520127745</v>
+        <v>-1.799703711263088</v>
       </c>
       <c r="G36">
-        <v>-10.2582065332033</v>
+        <v>-11.48514105769475</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.639380468629978</v>
       </c>
       <c r="E37">
-        <v>-33.03074130186928</v>
+        <v>-34.24903892838984</v>
       </c>
       <c r="F37">
-        <v>-1.644734394282163</v>
+        <v>-1.774415311190425</v>
       </c>
       <c r="G37">
-        <v>-10.25424049964725</v>
+        <v>-12.10695089469944</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.009628062461623</v>
       </c>
       <c r="E38">
-        <v>-32.63059854584051</v>
+        <v>-33.19591739129905</v>
       </c>
       <c r="F38">
-        <v>-1.706995316643976</v>
+        <v>-1.861562875434544</v>
       </c>
       <c r="G38">
-        <v>-10.95693689581296</v>
+        <v>-12.0394488711537</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.353295009912091</v>
       </c>
       <c r="E39">
-        <v>-31.91961001274023</v>
+        <v>-32.78850869872497</v>
       </c>
       <c r="F39">
-        <v>-1.482962524189447</v>
+        <v>-1.652131715189162</v>
       </c>
       <c r="G39">
-        <v>-11.08761405988461</v>
+        <v>-12.0319372433251</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.662275326079942</v>
       </c>
       <c r="E40">
-        <v>-31.49141788870796</v>
+        <v>-32.73399266438364</v>
       </c>
       <c r="F40">
-        <v>-1.464811337659304</v>
+        <v>-1.552529647043952</v>
       </c>
       <c r="G40">
-        <v>-10.67797708649181</v>
+        <v>-11.79314759357747</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.927184241505585</v>
       </c>
       <c r="E41">
-        <v>-31.1447677318948</v>
+        <v>-32.46721346788077</v>
       </c>
       <c r="F41">
-        <v>-1.382974436834533</v>
+        <v>-1.812891320315656</v>
       </c>
       <c r="G41">
-        <v>-10.30619289079504</v>
+        <v>-11.7814415045506</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.1398265871155</v>
       </c>
       <c r="E42">
-        <v>-30.46842881766421</v>
+        <v>-31.39440212580463</v>
       </c>
       <c r="F42">
-        <v>-1.469219908977003</v>
+        <v>-1.63771480891084</v>
       </c>
       <c r="G42">
-        <v>-10.70238904929839</v>
+        <v>-11.43273843235363</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.299514725638097</v>
       </c>
       <c r="E43">
-        <v>-30.93245928499319</v>
+        <v>-31.28260315950327</v>
       </c>
       <c r="F43">
-        <v>-1.524344446163699</v>
+        <v>-1.460709262280641</v>
       </c>
       <c r="G43">
-        <v>-10.64161405428846</v>
+        <v>-11.76425977320179</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.405283806263879</v>
       </c>
       <c r="E44">
-        <v>-29.62063734902922</v>
+        <v>-31.14613985951912</v>
       </c>
       <c r="F44">
-        <v>-1.396114828945141</v>
+        <v>-1.578892439638047</v>
       </c>
       <c r="G44">
-        <v>-10.67560673588569</v>
+        <v>-11.96273028882663</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.458276615372451</v>
       </c>
       <c r="E45">
-        <v>-29.45303173329433</v>
+        <v>-30.20365120667273</v>
       </c>
       <c r="F45">
-        <v>-1.353023985018914</v>
+        <v>-1.633488478421756</v>
       </c>
       <c r="G45">
-        <v>-10.4946754905279</v>
+        <v>-11.95404010678605</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.466868962826014</v>
       </c>
       <c r="E46">
-        <v>-27.82786883108061</v>
+        <v>-30.21900726203274</v>
       </c>
       <c r="F46">
-        <v>-1.390132359562123</v>
+        <v>-1.401194377859108</v>
       </c>
       <c r="G46">
-        <v>-10.46323523954144</v>
+        <v>-12.56378300530009</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.44200406887961</v>
       </c>
       <c r="E47">
-        <v>-27.61635286713035</v>
+        <v>-29.69385824525924</v>
       </c>
       <c r="F47">
-        <v>-1.366114675085354</v>
+        <v>-1.532081397705847</v>
       </c>
       <c r="G47">
-        <v>-10.64058447462574</v>
+        <v>-12.32662545450332</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.393775656170599</v>
       </c>
       <c r="E48">
-        <v>-26.75404537506377</v>
+        <v>-30.00405645054765</v>
       </c>
       <c r="F48">
-        <v>-1.283110604590038</v>
+        <v>-1.465727512006801</v>
       </c>
       <c r="G48">
-        <v>-10.68895154495449</v>
+        <v>-11.88168813402527</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.333726412339912</v>
       </c>
       <c r="E49">
-        <v>-27.27994611852254</v>
+        <v>-28.59419531655463</v>
       </c>
       <c r="F49">
-        <v>-1.269689395929881</v>
+        <v>-1.324065088984446</v>
       </c>
       <c r="G49">
-        <v>-10.66418204322967</v>
+        <v>-12.13103511349764</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.275608139938862</v>
       </c>
       <c r="E50">
-        <v>-26.38679971846372</v>
+        <v>-27.7675223864544</v>
       </c>
       <c r="F50">
-        <v>-1.251026278344808</v>
+        <v>-1.613653220961722</v>
       </c>
       <c r="G50">
-        <v>-10.56241587335247</v>
+        <v>-11.82216121468364</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.226892797428167</v>
       </c>
       <c r="E51">
-        <v>-25.73354470048724</v>
+        <v>-27.86301884632815</v>
       </c>
       <c r="F51">
-        <v>-1.22372743058555</v>
+        <v>-1.466381922255012</v>
       </c>
       <c r="G51">
-        <v>-10.83759835021331</v>
+        <v>-12.42322717333925</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.193241159012747</v>
       </c>
       <c r="E52">
-        <v>-26.04363195816246</v>
+        <v>-26.16981335791219</v>
       </c>
       <c r="F52">
-        <v>-1.011276042789561</v>
+        <v>-1.26409957269579</v>
       </c>
       <c r="G52">
-        <v>-10.54319153540592</v>
+        <v>-12.18661255201092</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.181611608384523</v>
       </c>
       <c r="E53">
-        <v>-25.51993658154543</v>
+        <v>-26.51406795197529</v>
       </c>
       <c r="F53">
-        <v>-1.290405207939091</v>
+        <v>-1.277066836019213</v>
       </c>
       <c r="G53">
-        <v>-10.68481998412148</v>
+        <v>-12.06437727906441</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.195269184315491</v>
       </c>
       <c r="E54">
-        <v>-24.73114433651936</v>
+        <v>-26.52980892762595</v>
       </c>
       <c r="F54">
-        <v>-1.216966295843901</v>
+        <v>-0.9968044642626537</v>
       </c>
       <c r="G54">
-        <v>-10.62322066327226</v>
+        <v>-12.39798757414785</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.233803337916944</v>
       </c>
       <c r="E55">
-        <v>-24.29903281823345</v>
+        <v>-26.01220434854923</v>
       </c>
       <c r="F55">
-        <v>-1.265315616043099</v>
+        <v>-1.434719235017807</v>
       </c>
       <c r="G55">
-        <v>-10.67839090468422</v>
+        <v>-12.3538017228352</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.297830323263953</v>
       </c>
       <c r="E56">
-        <v>-23.62770013201834</v>
+        <v>-25.56732253356169</v>
       </c>
       <c r="F56">
-        <v>-1.18300903090094</v>
+        <v>-1.394336324131331</v>
       </c>
       <c r="G56">
-        <v>-11.00534038214264</v>
+        <v>-12.22197248891588</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.389489281932317</v>
       </c>
       <c r="E57">
-        <v>-23.68931454936671</v>
+        <v>-25.75514552150382</v>
       </c>
       <c r="F57">
-        <v>-1.340989463391043</v>
+        <v>-1.108117990748643</v>
       </c>
       <c r="G57">
-        <v>-11.12134520838424</v>
+        <v>-12.71759757214571</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.505345246983262</v>
       </c>
       <c r="E58">
-        <v>-23.20652940693496</v>
+        <v>-24.70654113723569</v>
       </c>
       <c r="F58">
-        <v>-1.33599109448255</v>
+        <v>-1.533884753541741</v>
       </c>
       <c r="G58">
-        <v>-11.34092707291302</v>
+        <v>-12.89140783404853</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.64179538616157</v>
       </c>
       <c r="E59">
-        <v>-22.77628361994021</v>
+        <v>-24.44170692031911</v>
       </c>
       <c r="F59">
-        <v>-1.422930738508567</v>
+        <v>-1.561970550333658</v>
       </c>
       <c r="G59">
-        <v>-11.31419772822895</v>
+        <v>-12.50651718856178</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.799555802078173</v>
       </c>
       <c r="E60">
-        <v>-22.80011697864258</v>
+        <v>-23.80037537440482</v>
       </c>
       <c r="F60">
-        <v>-1.388569230273041</v>
+        <v>-1.75579278360809</v>
       </c>
       <c r="G60">
-        <v>-11.49652602380431</v>
+        <v>-13.16711006655903</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.977054855591312</v>
       </c>
       <c r="E61">
-        <v>-22.13703064359544</v>
+        <v>-23.76873945498724</v>
       </c>
       <c r="F61">
-        <v>-1.368259318291202</v>
+        <v>-1.553324051383237</v>
       </c>
       <c r="G61">
-        <v>-11.50605708441187</v>
+        <v>-12.83985270836545</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.169659984221034</v>
       </c>
       <c r="E62">
-        <v>-21.73203109919345</v>
+        <v>-23.82768660114508</v>
       </c>
       <c r="F62">
-        <v>-1.659470222010563</v>
+        <v>-1.766754569449335</v>
       </c>
       <c r="G62">
-        <v>-11.16362749601181</v>
+        <v>-13.15905881980752</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.373553454585923</v>
       </c>
       <c r="E63">
-        <v>-21.93826233397676</v>
+        <v>-23.89656921927575</v>
       </c>
       <c r="F63">
-        <v>-1.688764606843165</v>
+        <v>-1.889017456265528</v>
       </c>
       <c r="G63">
-        <v>-11.89442711326039</v>
+        <v>-13.65540725723768</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.587945103004131</v>
       </c>
       <c r="E64">
-        <v>-21.86195754694752</v>
+        <v>-22.78208912361804</v>
       </c>
       <c r="F64">
-        <v>-1.63759055380042</v>
+        <v>-1.888059863547892</v>
       </c>
       <c r="G64">
-        <v>-11.69729074748787</v>
+        <v>-13.19915283683364</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.805842106197042</v>
       </c>
       <c r="E65">
-        <v>-21.54653574689126</v>
+        <v>-23.75254563193581</v>
       </c>
       <c r="F65">
-        <v>-1.626571610608381</v>
+        <v>-1.925373673206996</v>
       </c>
       <c r="G65">
-        <v>-11.81086232275811</v>
+        <v>-13.750123620389</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.019063029931871</v>
       </c>
       <c r="E66">
-        <v>-20.50323420568611</v>
+        <v>-22.43532122648068</v>
       </c>
       <c r="F66">
-        <v>-1.781646130249462</v>
+        <v>-2.097076840091875</v>
       </c>
       <c r="G66">
-        <v>-12.11688584186279</v>
+        <v>-13.42199889926414</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.224314845884424</v>
       </c>
       <c r="E67">
-        <v>-20.54508636246499</v>
+        <v>-22.98565761568485</v>
       </c>
       <c r="F67">
-        <v>-2.110495563649824</v>
+        <v>-1.986987640627223</v>
       </c>
       <c r="G67">
-        <v>-12.2082502776556</v>
+        <v>-13.03537683846035</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.414752237404263</v>
       </c>
       <c r="E68">
-        <v>-21.67607274588067</v>
+        <v>-22.45507443010214</v>
       </c>
       <c r="F68">
-        <v>-2.007029989937957</v>
+        <v>-2.121106950079685</v>
       </c>
       <c r="G68">
-        <v>-11.81492436213479</v>
+        <v>-13.73975830230554</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.581591610583128</v>
       </c>
       <c r="E69">
-        <v>-21.07500839084258</v>
+        <v>-22.4956088009448</v>
       </c>
       <c r="F69">
-        <v>-2.272819126432803</v>
+        <v>-2.300781496481704</v>
       </c>
       <c r="G69">
-        <v>-11.72885348865928</v>
+        <v>-13.68235840847289</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.718980479690341</v>
       </c>
       <c r="E70">
-        <v>-21.01594350436054</v>
+        <v>-23.27264059897294</v>
       </c>
       <c r="F70">
-        <v>-2.324507595632687</v>
+        <v>-2.281205518018746</v>
       </c>
       <c r="G70">
-        <v>-11.70283922181169</v>
+        <v>-13.03322167331429</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.82469088459777</v>
       </c>
       <c r="E71">
-        <v>-20.65362935595484</v>
+        <v>-21.89384706090953</v>
       </c>
       <c r="F71">
-        <v>-2.253017003668881</v>
+        <v>-2.592706452902278</v>
       </c>
       <c r="G71">
-        <v>-11.58553666171869</v>
+        <v>-12.89245065589339</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.892125330038658</v>
       </c>
       <c r="E72">
-        <v>-20.5164573497885</v>
+        <v>-21.90856460143446</v>
       </c>
       <c r="F72">
-        <v>-2.280334075511001</v>
+        <v>-2.670639258157655</v>
       </c>
       <c r="G72">
-        <v>-11.76286272298421</v>
+        <v>-12.92582095492925</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.917717151402101</v>
       </c>
       <c r="E73">
-        <v>-20.39567841952993</v>
+        <v>-22.57934934229464</v>
       </c>
       <c r="F73">
-        <v>-2.333674309312066</v>
+        <v>-2.377188448981125</v>
       </c>
       <c r="G73">
-        <v>-11.47044223550039</v>
+        <v>-13.16388228465824</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.903266645072513</v>
       </c>
       <c r="E74">
-        <v>-21.01376077988884</v>
+        <v>-22.71310235058519</v>
       </c>
       <c r="F74">
-        <v>-2.508456517833151</v>
+        <v>-2.803670921210242</v>
       </c>
       <c r="G74">
-        <v>-11.5102581667012</v>
+        <v>-13.1341635173522</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.847606327875059</v>
       </c>
       <c r="E75">
-        <v>-21.58262315625838</v>
+        <v>-22.91367299285892</v>
       </c>
       <c r="F75">
-        <v>-2.595362198795653</v>
+        <v>-2.869351344210812</v>
       </c>
       <c r="G75">
-        <v>-10.84398108201302</v>
+        <v>-12.88905072562456</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.750158426504177</v>
       </c>
       <c r="E76">
-        <v>-21.31080603242198</v>
+        <v>-23.19482783009914</v>
       </c>
       <c r="F76">
-        <v>-2.750491390685319</v>
+        <v>-2.703957851833057</v>
       </c>
       <c r="G76">
-        <v>-11.65349885109439</v>
+        <v>-12.37856791401449</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.614408704405706</v>
       </c>
       <c r="E77">
-        <v>-21.18028182609889</v>
+        <v>-23.90387364785013</v>
       </c>
       <c r="F77">
-        <v>-2.855847298810374</v>
+        <v>-2.712174428101425</v>
       </c>
       <c r="G77">
-        <v>-11.31354886130325</v>
+        <v>-12.67097846986169</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.445115307770443</v>
       </c>
       <c r="E78">
-        <v>-21.89814911121682</v>
+        <v>-23.79393588436592</v>
       </c>
       <c r="F78">
-        <v>-2.900377845282667</v>
+        <v>-2.887417208898466</v>
       </c>
       <c r="G78">
-        <v>-11.15093155386871</v>
+        <v>-12.49249371765742</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.242452808649789</v>
       </c>
       <c r="E79">
-        <v>-22.19339655956891</v>
+        <v>-23.90992368912438</v>
       </c>
       <c r="F79">
-        <v>-2.797931991843646</v>
+        <v>-2.971339938843487</v>
       </c>
       <c r="G79">
-        <v>-10.37726699297765</v>
+        <v>-12.25526002431325</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.012273493597878</v>
       </c>
       <c r="E80">
-        <v>-22.71389483353654</v>
+        <v>-23.92319664644086</v>
       </c>
       <c r="F80">
-        <v>-2.837679544932175</v>
+        <v>-3.291402050834952</v>
       </c>
       <c r="G80">
-        <v>-10.678457115595</v>
+        <v>-12.10280940222981</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.76322902051452</v>
       </c>
       <c r="E81">
-        <v>-23.28605393898366</v>
+        <v>-24.66823930407882</v>
       </c>
       <c r="F81">
-        <v>-3.009274195687287</v>
+        <v>-3.04762346459989</v>
       </c>
       <c r="G81">
-        <v>-10.14262876733627</v>
+        <v>-12.03633364780125</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-7.500709693382754</v>
       </c>
       <c r="E82">
-        <v>-23.52236329812592</v>
+        <v>-25.49918258516827</v>
       </c>
       <c r="F82">
-        <v>-2.918169520359995</v>
+        <v>-3.214626474841285</v>
       </c>
       <c r="G82">
-        <v>-10.06286117256753</v>
+        <v>-11.67435859853734</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-7.231590765790047</v>
       </c>
       <c r="E83">
-        <v>-24.57180092161147</v>
+        <v>-26.01952236254563</v>
       </c>
       <c r="F83">
-        <v>-2.904194133907365</v>
+        <v>-3.225393594342873</v>
       </c>
       <c r="G83">
-        <v>-9.540993394847895</v>
+        <v>-11.66725085726452</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.966697686095277</v>
       </c>
       <c r="E84">
-        <v>-25.22190865015262</v>
+        <v>-26.48321545856103</v>
       </c>
       <c r="F84">
-        <v>-3.286503914382198</v>
+        <v>-3.13591334749247</v>
       </c>
       <c r="G84">
-        <v>-9.692867982007501</v>
+        <v>-11.32765840639162</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.716579489355221</v>
       </c>
       <c r="E85">
-        <v>-25.30160526421361</v>
+        <v>-27.49303346295347</v>
       </c>
       <c r="F85">
-        <v>-3.116228024532343</v>
+        <v>-3.20079770941895</v>
       </c>
       <c r="G85">
-        <v>-10.05670024731894</v>
+        <v>-11.08247278266212</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.486930422372596</v>
       </c>
       <c r="E86">
-        <v>-26.21229950105215</v>
+        <v>-28.05330532413046</v>
       </c>
       <c r="F86">
-        <v>-3.529523716076294</v>
+        <v>-3.358126216763049</v>
       </c>
       <c r="G86">
-        <v>-9.546316752075043</v>
+        <v>-11.41816541088976</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.28768168810417</v>
       </c>
       <c r="E87">
-        <v>-27.76152668686824</v>
+        <v>-29.49518503359473</v>
       </c>
       <c r="F87">
-        <v>-3.367239914928649</v>
+        <v>-3.377942421772818</v>
       </c>
       <c r="G87">
-        <v>-9.371304762141472</v>
+        <v>-11.21007113938225</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.130692095735213</v>
       </c>
       <c r="E88">
-        <v>-27.74286937395664</v>
+        <v>-29.8272036908891</v>
       </c>
       <c r="F88">
-        <v>-3.37178516686781</v>
+        <v>-3.676215157601045</v>
       </c>
       <c r="G88">
-        <v>-9.302915512391207</v>
+        <v>-11.29083851890385</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.022194419812734</v>
       </c>
       <c r="E89">
-        <v>-30.13859967755254</v>
+        <v>-31.03535979986948</v>
       </c>
       <c r="F89">
-        <v>-3.658585842534666</v>
+        <v>-3.521703099426464</v>
       </c>
       <c r="G89">
-        <v>-9.583745779942044</v>
+        <v>-10.41059094437595</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.967527288534852</v>
       </c>
       <c r="E90">
-        <v>-30.48126477723896</v>
+        <v>-31.49041483171526</v>
       </c>
       <c r="F90">
-        <v>-3.494694180258187</v>
+        <v>-3.786857706490767</v>
       </c>
       <c r="G90">
-        <v>-9.666595492607843</v>
+        <v>-11.04028319030965</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.972647197525115</v>
       </c>
       <c r="E91">
-        <v>-31.90502379796153</v>
+        <v>-32.83098804915393</v>
       </c>
       <c r="F91">
-        <v>-4.065739189786859</v>
+        <v>-3.731085385995081</v>
       </c>
       <c r="G91">
-        <v>-9.59243596198263</v>
+        <v>-10.86207983447622</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.042091310155008</v>
       </c>
       <c r="E92">
-        <v>-33.21865033081755</v>
+        <v>-35.54349190229738</v>
       </c>
       <c r="F92">
-        <v>-3.835014845452516</v>
+        <v>-3.797119521876647</v>
       </c>
       <c r="G92">
-        <v>-9.453359943877848</v>
+        <v>-11.36949045982585</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.172238425219588</v>
       </c>
       <c r="E93">
-        <v>-34.64549097810234</v>
+        <v>-36.54950372428637</v>
       </c>
       <c r="F93">
-        <v>-3.793094484666444</v>
+        <v>-4.030441626386169</v>
       </c>
       <c r="G93">
-        <v>-9.495724995143901</v>
+        <v>-11.46525461064035</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.357243077179006</v>
       </c>
       <c r="E94">
-        <v>-36.37152111036291</v>
+        <v>-37.37736085033961</v>
       </c>
       <c r="F94">
-        <v>-3.740442624177104</v>
+        <v>-4.227028121683743</v>
       </c>
       <c r="G94">
-        <v>-10.09593352250485</v>
+        <v>-11.51028134051998</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.592874988637735</v>
       </c>
       <c r="E95">
-        <v>-38.04474017874602</v>
+        <v>-38.54079148578323</v>
       </c>
       <c r="F95">
-        <v>-4.245085702697369</v>
+        <v>-4.123106945900336</v>
       </c>
       <c r="G95">
-        <v>-9.690044086662501</v>
+        <v>-11.67706000369738</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-6.866934023629806</v>
       </c>
       <c r="E96">
-        <v>-39.06399099449643</v>
+        <v>-41.04952080129253</v>
       </c>
       <c r="F96">
-        <v>-4.078539122894917</v>
+        <v>-4.363953111529487</v>
       </c>
       <c r="G96">
-        <v>-10.27996674903293</v>
+        <v>-11.54400255738299</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-7.162307134901615</v>
       </c>
       <c r="E97">
-        <v>-41.35063715195857</v>
+        <v>-42.3983607480322</v>
       </c>
       <c r="F97">
-        <v>-4.27804892675697</v>
+        <v>-4.586265384888401</v>
       </c>
       <c r="G97">
-        <v>-10.44047192841342</v>
+        <v>-11.83155985346963</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-7.464824022190758</v>
       </c>
       <c r="E98">
-        <v>-43.40119131703081</v>
+        <v>-44.09346819553139</v>
       </c>
       <c r="F98">
-        <v>-4.40200333980968</v>
+        <v>-4.743832462044507</v>
       </c>
       <c r="G98">
-        <v>-10.92478156699002</v>
+        <v>-12.49261951838792</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.756720802916912</v>
       </c>
       <c r="E99">
-        <v>-45.07473190706846</v>
+        <v>-45.01365637812701</v>
       </c>
       <c r="F99">
-        <v>-4.357394926801523</v>
+        <v>-4.570673025265506</v>
       </c>
       <c r="G99">
-        <v>-10.87231604128365</v>
+        <v>-12.64786755145204</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-8.022483672517641</v>
       </c>
       <c r="E100">
-        <v>-46.66769962332464</v>
+        <v>-47.80783805270981</v>
       </c>
       <c r="F100">
-        <v>-4.438246898784366</v>
+        <v>-4.979720848767903</v>
       </c>
       <c r="G100">
-        <v>-11.02824604672886</v>
+        <v>-13.64782445267998</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.236844015429277</v>
       </c>
       <c r="E101">
-        <v>-48.54195123833026</v>
+        <v>-48.97552885007615</v>
       </c>
       <c r="F101">
-        <v>-4.752755635707463</v>
+        <v>-4.876798684072272</v>
       </c>
       <c r="G101">
-        <v>-11.55324891107418</v>
+        <v>-12.83545299334376</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.401198600063147</v>
       </c>
       <c r="E102">
-        <v>-50.72859736851801</v>
+        <v>-51.50918515076068</v>
       </c>
       <c r="F102">
-        <v>-4.875077336609254</v>
+        <v>-5.09248981678061</v>
       </c>
       <c r="G102">
-        <v>-11.45183696956969</v>
+        <v>-13.51679637078117</v>
       </c>
     </row>
   </sheetData>
